--- a/ARM Functions/Other Mechanics/Ability Expansion.xlsx
+++ b/ARM Functions/Other Mechanics/Ability Expansion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E34E680-887D-45D1-AC5F-14EDC38C2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E963DFE-BD25-4783-8F01-94667E08F377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{AB739BBE-2783-4764-B01D-DC4A38DD392E}"/>
+    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{AB739BBE-2783-4764-B01D-DC4A38DD392E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="77">
   <si>
     <t>File</t>
   </si>
@@ -110,9 +110,6 @@
     <t>B020D1E1</t>
   </si>
   <si>
-    <t>0032339c</t>
-  </si>
-  <si>
     <t>Battle.cro</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
     <t>00031828</t>
   </si>
   <si>
-    <t>70E828</t>
-  </si>
-  <si>
     <t>0004BD28</t>
   </si>
   <si>
@@ -207,13 +201,79 @@
   </si>
   <si>
     <t>new</t>
+  </si>
+  <si>
+    <t>Load Ability 1</t>
+  </si>
+  <si>
+    <t>Load Ability 2</t>
+  </si>
+  <si>
+    <t>Load Ability 3</t>
+  </si>
+  <si>
+    <t>004AB288</t>
+  </si>
+  <si>
+    <t>004AB294</t>
+  </si>
+  <si>
+    <t>004AB27C</t>
+  </si>
+  <si>
+    <t>B801D0E1</t>
+  </si>
+  <si>
+    <t>BA01D0E1</t>
+  </si>
+  <si>
+    <t>(now 0x18-19)</t>
+  </si>
+  <si>
+    <t>(now 0x1A-1B, 2nd byte is the basically unused Flee rate)</t>
+  </si>
+  <si>
+    <t>(now 0x4A-0x4B)</t>
+  </si>
+  <si>
+    <t>BA04D0E1</t>
+  </si>
+  <si>
+    <t>0032339C</t>
+  </si>
+  <si>
+    <t>1800D0E5</t>
+  </si>
+  <si>
+    <t>1900D0E5</t>
+  </si>
+  <si>
+    <t>1A00D0E5</t>
+  </si>
+  <si>
+    <t>004CE0D8</t>
+  </si>
+  <si>
+    <t>00F020E3</t>
+  </si>
+  <si>
+    <t>0031DAD0</t>
+  </si>
+  <si>
+    <t>0031DAE0</t>
+  </si>
+  <si>
+    <t>0031DAF4</t>
+  </si>
+  <si>
+    <t>0070E828</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +286,12 @@
       <color theme="1"/>
       <name val="Cascadia Code"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -598,12 +664,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9942FA2A-BBE7-4EA9-AF7E-D6224FE258DA}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="2" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.35546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.35546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.35546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="1"/>
@@ -617,18 +683,18 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
@@ -642,10 +708,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -659,10 +725,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -676,10 +742,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -693,13 +759,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
@@ -710,13 +776,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>14</v>
@@ -727,13 +793,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>6</v>
@@ -744,13 +810,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -761,13 +827,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>18</v>
@@ -778,10 +844,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -796,10 +862,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>21</v>
@@ -814,13 +880,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>16</v>
@@ -831,13 +897,13 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>12</v>
@@ -848,13 +914,13 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>22</v>
@@ -866,13 +932,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>16</v>
@@ -881,15 +947,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>12</v>
@@ -898,15 +964,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>12</v>
@@ -915,22 +981,22 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f t="shared" ref="B3:B27" si="0">DEC2HEX(HEX2DEC(C19)-HEX2DEC("6dd000"),8)</f>
+        <f t="shared" ref="B19:B27" si="0">DEC2HEX(HEX2DEC(C19)-HEX2DEC("6dd000"),8)</f>
         <v>FFFF923000</v>
       </c>
       <c r="C19" s="1" t="str">
-        <f t="shared" ref="C18:C27" si="1">UPPER(F19)</f>
+        <f t="shared" ref="C19:C27" si="1">UPPER(F19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="1" t="str">
         <f t="shared" si="0"/>
@@ -941,9 +1007,9 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -954,9 +1020,9 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1" t="str">
         <f t="shared" si="0"/>
@@ -967,9 +1033,9 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1" t="str">
         <f t="shared" si="0"/>
@@ -980,9 +1046,9 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1" t="str">
         <f t="shared" si="0"/>
@@ -993,9 +1059,9 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1006,9 +1072,9 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1019,9 +1085,9 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1032,17 +1098,16 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="1" t="str">
         <f>DEC2HEX(HEX2DEC(C29)-HEX2DEC("0100000"),8)</f>
         <v>0022339C</v>
       </c>
-      <c r="C29" s="1" t="str">
-        <f>UPPER(F29)</f>
-        <v>0032339C</v>
+      <c r="C29" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>12</v>
@@ -1050,12 +1115,154 @@
       <c r="E29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>24</v>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(C30)-HEX2DEC("0100000"),8)</f>
+        <v>003AB27C</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(C31)-HEX2DEC("0100000"),8)</f>
+        <v>003AB288</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(C32)-HEX2DEC("0100000"),8)</f>
+        <v>003AB294</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(C33)-HEX2DEC("0100000"),8)</f>
+        <v>003CE0D8</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="1" t="str">
+        <f t="shared" ref="B34:B36" si="2">DEC2HEX(HEX2DEC(C34)-HEX2DEC("0100000"),8)</f>
+        <v>0021DAD0</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>0021DAE0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>0021DAF4</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C1048576">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="C1:C32 C34:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
